--- a/report_forms/050_digital_audit_trail_report_form--report_forms.xlsx
+++ b/report_forms/050_digital_audit_trail_report_form--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_1</t>
+          <t>activity_details</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -528,10 +528,14 @@
           <t>Activity Details</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Briefly describe the activity that occurred.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,7 +547,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_2</t>
+          <t>report_details</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -551,7 +555,11 @@
           <t>Report Details</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select all relevant report details.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -561,12 +569,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_3</t>
+          <t>user_details</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -574,10 +582,14 @@
           <t>User Details</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enter user information.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,7 +601,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_4</t>
+          <t>additional_info</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -597,7 +609,11 @@
           <t>Additional Information</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Enter any additional relevant information.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -612,7 +628,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_5</t>
+          <t>date_and_time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -620,76 +636,92 @@
           <t>Date and Time</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Enter the date and time of the activity.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_6</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Date and Time</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>User ID</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enter user ID.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_7</t>
+          <t>ip_address</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Date and Time</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>IP Address</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Enter IP address.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_8</t>
+          <t>device_type</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Date and Time</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Device Type</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select device type.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -699,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_9</t>
+          <t>device_os</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Date and Time</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Device OS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select device OS.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -722,20 +758,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_10</t>
+          <t>browser_type</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Date and Time</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Browser Type</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Select browser type.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -745,20 +785,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_11</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Date and Time</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Enter location.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,20 +812,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_12</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Date and Time</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Add any notes about the activity.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -791,20 +839,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_13</t>
+          <t>date_and_time_activity</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Date and Time</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Date and Time Activity</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Select date and time of activity.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -814,20 +866,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_14</t>
+          <t>activity_type</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Date and Time</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Activity Type</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Select activity type.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -837,20 +893,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_15</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Date and Time</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Select status.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -860,20 +920,24 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_16</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Date and Time</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Enter comments.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -883,23 +947,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_17</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Date and Time</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Enter date.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,179 +979,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_18</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Date and Time</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Enter time.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>digital_audit_trail_report_form_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Date and Time</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>digital_audit_trail_report_form_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Date and Time</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>digital_audit_trail_report_form_page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Date and Time</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>digital_audit_trail_report_form_page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Date and Time</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>digital_audit_trail_report_form_page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Date and Time</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>digital_audit_trail_report_form_page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Date and Time</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>digital_audit_trail_report_form_page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Date and Time</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1009,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,153 +1037,425 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_2_choices</t>
+          <t>report_details_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>item_1</t>
+          <t>report_type_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Item 1</t>
+          <t>Report Type 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_2_choices</t>
+          <t>report_details_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>item_2</t>
+          <t>report_type_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Item 2</t>
+          <t>Report Type 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_2_choices</t>
+          <t>report_details_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>item_3</t>
+          <t>report_type_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Item 3</t>
+          <t>Report Type 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_3_choices</t>
+          <t>device_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>desktop</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Desktop</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_3_choices</t>
+          <t>device_type_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_3_choices</t>
+          <t>device_type_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>tablet</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Tablet</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_3_choices</t>
+          <t>device_type_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>console</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Console</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_3_choices</t>
+          <t>device_os_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>windows</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Windows</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>digital_audit_trail_report_form_page_3_choices</t>
+          <t>device_os_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>macos</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>MacOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>device_os_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>linux</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Linux</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>device_os_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>android</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>browser_type_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>chrome</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Chrome</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>browser_type_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>firefox</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Firefox</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>browser_type_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>safari</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Safari</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>browser_type_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ie</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>date_and_time_activity_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>yesterday</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Yesterday</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>date_and_time_activity_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Today</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>date_and_time_activity_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>tomorrow</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Tomorrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>date_and_time_activity_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>this_week</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>This week</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>activity_type_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>activity_1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Activity 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>activity_type_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>activity_2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Activity 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>activity_type_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>activity_3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Activity 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>status_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>status_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>status_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>in_progress</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
